--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12926,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12980,6 +12998,69 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>CLUB_S2008_09_0232</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2008_09_0206 'HC Jiskra Humpolec B' prev→CLUB_S2007_08_0119 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0021</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2008_09_0021 'Baráž o Extraligu' (L15, parent=NODE_S2008_09_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0028</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2008_09_0028 'Baráž o I.ligu' (L25, parent=NODE_S2008_09_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0042</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2008_09_0042 'O postup do I.ligy' (L25, parent=NODE_S2008_09_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -16284,8 +16365,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -16365,7 +16444,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
@@ -32596,6 +32674,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0206</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0206 'HC Jiskra Humpolec B' prev→CLUB_S2007_08_0119 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0021</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2008_09_0021 'Baráž o Extraligu' (L15, parent=NODE_S2008_09_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0028</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2008_09_0028 'Baráž o I.ligu' (L25, parent=NODE_S2008_09_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0042</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2008_09_0042 'O postup do I.ligy' (L25, parent=NODE_S2008_09_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12944,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13004,7 +13004,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2008_09_0206 'HC Jiskra Humpolec B' prev→CLUB_S2007_08_0119 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13014,14 +13014,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0021</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2008_09_0021 'Baráž o Extraligu' (L15, parent=NODE_S2008_09_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13031,14 +13026,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0028</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2008_09_0028 'Baráž o I.ligu' (L25, parent=NODE_S2008_09_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13048,17 +13038,435 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0042</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2008_09_0042 'O postup do I.ligy' (L25, parent=NODE_S2008_09_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Veverská Bitýška' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0030</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0031</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0032</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16365,6 +16773,8 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -16395,6 +16805,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0001</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16407,6 +16822,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0003</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16419,6 +16839,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0003</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16431,6 +16856,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0036</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16444,6 +16874,7 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
@@ -23536,12 +23967,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -23578,12 +24009,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -23709,12 +24140,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -23840,12 +24271,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -23971,12 +24402,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -24181,12 +24612,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -24813,12 +25244,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -25149,12 +25580,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tábor = Hockey Club Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. city Tábor.</t>
+          <t>Tábor = Hockey Club Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. city Tábor. || TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Hockey Club Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -25275,12 +25706,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -25317,12 +25748,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -25406,12 +25837,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -25448,12 +25879,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa.</t>
+          <t>Česká Lípa = HC Predators Česká Lípa (Wiki D42 - registr ustavy 04/2026). Liberecky kraj. Post-revolucni anglicky nazev. city Česká Lípa. || TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Predators Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -25616,12 +26047,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -25742,12 +26173,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
     </row>
@@ -26167,12 +26598,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Vsetín = Valašský hokejový klub Vsetín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. **VHK** = Valašský hokejový klub. city Vsetín.</t>
+          <t>Vsetín = Valašský hokejový klub Vsetín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. **VHK** = Valašský hokejový klub. city Vsetín. || TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Valašský hokejový klub Vsetín</t>
+          <t>Vsetín</t>
         </is>
       </c>
     </row>
@@ -26251,12 +26682,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -26854,12 +27285,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -26980,12 +27411,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -27704,12 +28135,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -27788,12 +28219,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28203,12 +28634,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29552,12 +29983,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -29594,12 +30025,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -29720,12 +30151,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -30424,12 +30855,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Veverská Bitýška' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Veverská Bitýška</t>
         </is>
       </c>
     </row>
@@ -31737,12 +32168,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -32466,12 +32897,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -32680,11 +33111,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -32729,21 +33160,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0206</t>
+          <t>CLUB_S2008_09_0010</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0206 'HC Jiskra Humpolec B' prev→CLUB_S2007_08_0119 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -32751,21 +33180,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S2008_09_0021</t>
+          <t>CLUB_S2008_09_0011</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2008_09_0021 'Baráž o Extraligu' (L15, parent=NODE_S2008_09_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -32773,21 +33200,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S2008_09_0028</t>
+          <t>CLUB_S2008_09_0014</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2008_09_0028 'Baráž o I.ligu' (L25, parent=NODE_S2008_09_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -32795,24 +33220,702 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S2008_09_0042</t>
+          <t>CLUB_S2008_09_0017</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2008_09_0042 'O postup do I.ligy' (L25, parent=NODE_S2008_09_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0020</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0025</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0045</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0053</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0057</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0058</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0060</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0061</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0065</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0068</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0094</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0097</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0114</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0114</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0116</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0126</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0135</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0142</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0158</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0161</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0162</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0165</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0167</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0177</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0184</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Veverská Bitýška' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0206</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0213</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0219</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0239</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0030</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0031</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0032</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12944,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13016,7 +13016,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13028,7 +13028,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13040,7 +13040,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13064,7 +13064,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13076,7 +13076,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13088,7 +13088,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13100,7 +13100,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13112,7 +13112,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13124,7 +13124,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13148,7 +13148,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13160,7 +13160,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13172,7 +13172,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -13196,7 +13196,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -13208,7 +13208,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13232,7 +13232,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13244,7 +13244,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -13256,7 +13256,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13268,7 +13268,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13280,7 +13280,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13290,9 +13290,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0030</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13302,9 +13307,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0031</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13314,159 +13324,17 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0032</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Veverská Bitýška' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0030</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0031</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0032</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -13541,7 +13409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13600,6 +13468,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13642,6 +13515,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: Energie Karlovy Vary.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13689,6 +13567,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13731,6 +13614,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13773,6 +13661,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13815,6 +13708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13857,6 +13755,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13899,6 +13802,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13941,6 +13849,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13983,6 +13896,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14025,6 +13943,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14067,6 +13990,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14109,6 +14037,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14151,6 +14084,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14193,6 +14131,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14235,6 +14178,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14277,6 +14225,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14319,6 +14272,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14361,6 +14319,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14403,6 +14366,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14445,6 +14413,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14487,6 +14460,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14529,6 +14507,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14571,6 +14554,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14613,6 +14601,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14655,6 +14648,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14697,6 +14695,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14739,6 +14742,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14781,6 +14789,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14828,6 +14841,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14860,6 +14878,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14892,6 +14915,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14966,6 +14994,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0032</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15092,6 +15125,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0035</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15134,6 +15172,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0036</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15176,6 +15219,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15218,6 +15266,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15260,6 +15313,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0039</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -15302,6 +15360,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0040</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15344,6 +15407,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0041</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15386,6 +15454,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0042</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15428,6 +15501,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0043</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15470,6 +15548,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0044</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15512,6 +15595,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0045</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15554,6 +15642,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0046</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15596,6 +15689,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0047</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15722,6 +15820,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0048</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15764,6 +15867,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0049</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15806,6 +15914,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0050</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15848,6 +15961,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0056</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15890,6 +16008,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15932,6 +16055,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0052</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15974,6 +16102,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0053</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16016,6 +16149,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0054</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16058,6 +16196,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0055</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16142,6 +16285,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0058</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16268,6 +16416,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0064</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16310,6 +16463,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0065</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16562,6 +16720,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0069</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16646,6 +16809,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0070</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16770,6 +16938,11 @@
       <c r="K77" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0073</t>
         </is>
       </c>
     </row>
@@ -16793,6 +16966,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -16810,6 +16988,11 @@
           <t>NODE_S2008_09_0001</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16827,6 +17010,11 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16844,6 +17032,11 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16861,6 +17054,11 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16871,6 +17069,11 @@
       <c r="B86" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -24009,12 +24212,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24140,12 +24343,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24402,12 +24605,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -25244,12 +25447,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26173,12 +26376,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SC Kolín</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -27411,12 +27614,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28135,12 +28338,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -28219,12 +28422,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -30855,12 +31058,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Veverská Bitýška' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Veverská Bitýška</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32168,12 +32371,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32897,12 +33100,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -33111,7 +33314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -33185,12 +33388,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0011</t>
+          <t>CLUB_S2008_09_0017</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33205,12 +33408,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0014</t>
+          <t>CLUB_S2008_09_0025</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33225,12 +33428,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0017</t>
+          <t>CLUB_S2008_09_0053</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33245,12 +33448,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0020</t>
+          <t>CLUB_S2008_09_0057</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33265,12 +33468,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0025</t>
+          <t>CLUB_S2008_09_0058</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33285,12 +33488,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0045</t>
+          <t>CLUB_S2008_09_0060</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33305,12 +33508,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0053</t>
+          <t>CLUB_S2008_09_0061</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33325,12 +33528,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0057</t>
+          <t>CLUB_S2008_09_0065</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33345,12 +33548,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0058</t>
+          <t>CLUB_S2008_09_0078</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33365,12 +33568,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0060</t>
+          <t>CLUB_S2008_09_0080</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33385,12 +33588,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0061</t>
+          <t>CLUB_S2008_09_0094</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33405,12 +33608,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0065</t>
+          <t>CLUB_S2008_09_0114</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33425,12 +33628,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0068</t>
+          <t>CLUB_S2008_09_0126</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33445,12 +33648,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0078</t>
+          <t>CLUB_S2008_09_0135</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -33465,12 +33668,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0080</t>
+          <t>CLUB_S2008_09_0142</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -33485,12 +33688,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0094</t>
+          <t>CLUB_S2008_09_0158</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -33505,12 +33708,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0097</t>
+          <t>CLUB_S2008_09_0161</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33525,12 +33728,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0114</t>
+          <t>CLUB_S2008_09_0162</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33545,12 +33748,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0114</t>
+          <t>CLUB_S2008_09_0165</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -33565,12 +33768,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0116</t>
+          <t>CLUB_S2008_09_0167</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -33585,12 +33788,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0126</t>
+          <t>CLUB_S2008_09_0177</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -33605,12 +33808,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0135</t>
+          <t>CLUB_S2008_09_0206</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -33625,12 +33828,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0142</t>
+          <t>CLUB_S2008_09_0213</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -33640,17 +33843,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0158</t>
+          <t>NODE_S2008_09_0030</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
     </row>
@@ -33660,17 +33863,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0161</t>
+          <t>NODE_S2008_09_0031</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
     </row>
@@ -33680,242 +33883,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2008_09_0162</t>
+          <t>NODE_S2008_09_0032</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0165</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0167</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0177</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0184</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Veverská Bitýška' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0206</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0213</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0219</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S2008_09_0239</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0030</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0031</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0032</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -12944,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13002,21 +13002,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] HC Benešov převedl po skončení soutěže licenci na TJ Spartak Vlašim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13028,7 +13033,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13040,7 +13045,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13052,7 +13057,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13064,7 +13069,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13076,7 +13081,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13088,7 +13093,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13100,7 +13105,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13112,7 +13117,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13124,7 +13129,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13136,7 +13141,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13148,7 +13153,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13160,7 +13165,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13172,7 +13177,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -13196,7 +13201,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -13208,7 +13213,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13220,7 +13225,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13232,7 +13237,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13244,7 +13249,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -13256,7 +13261,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13268,7 +13273,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13280,24 +13285,19 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NODE_S2008_09_0030</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13309,12 +13309,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NODE_S2008_09_0031</t>
+          <t>NODE_S2008_09_0030</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13326,15 +13326,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>NODE_S2008_09_0031</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>NODE_S2008_09_0032</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -41322,7 +41339,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / Finále / HC Benešov převedl po skončení soutěže licenci na TJ Spartak Vlašim</t>
+          <t>Krajský přebor / Finále</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -13426,7 +13426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13490,6 +13490,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16963,8 +16973,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -17094,7 +17102,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -13678,6 +13678,16 @@
           <t>NODE_S2008_09_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13692,6 +13702,14 @@
         <is>
           <t>NODE_S2007_08_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -13866,6 +13884,16 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13880,6 +13908,14 @@
         <is>
           <t>NODE_S2007_08_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13960,6 +13996,16 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13974,6 +14020,14 @@
         <is>
           <t>NODE_S2007_08_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -14007,6 +14061,16 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14021,6 +14085,14 @@
         <is>
           <t>NODE_S2007_08_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -14054,6 +14126,8 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14068,6 +14142,14 @@
         <is>
           <t>NODE_S2007_08_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -14101,6 +14183,8 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14115,6 +14199,14 @@
         <is>
           <t>NODE_S2007_08_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -14148,6 +14240,8 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14162,6 +14256,14 @@
         <is>
           <t>NODE_S2007_08_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -14195,6 +14297,8 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14209,6 +14313,14 @@
         <is>
           <t>NODE_S2007_08_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -14242,6 +14354,8 @@
           <t>NODE_S2008_09_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14256,6 +14370,14 @@
         <is>
           <t>NODE_S2007_08_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -14289,6 +14411,8 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14303,6 +14427,14 @@
         <is>
           <t>NODE_S2007_08_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -14336,6 +14468,8 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14350,6 +14484,14 @@
         <is>
           <t>NODE_S2007_08_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -14383,6 +14525,16 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14397,6 +14549,14 @@
         <is>
           <t>NODE_S2007_08_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -14524,6 +14684,16 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14538,6 +14708,14 @@
         <is>
           <t>NODE_S2007_08_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>16 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -14571,6 +14749,16 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14585,6 +14773,14 @@
         <is>
           <t>NODE_S2007_08_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14618,6 +14814,12 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14632,6 +14834,14 @@
         <is>
           <t>NODE_S2007_08_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -14665,6 +14875,12 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14679,6 +14895,14 @@
         <is>
           <t>NODE_S2007_08_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -14712,6 +14936,8 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14726,6 +14952,14 @@
         <is>
           <t>NODE_S2007_08_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -14759,6 +14993,8 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14773,6 +15009,14 @@
         <is>
           <t>NODE_S2007_08_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -15283,6 +15527,12 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15297,6 +15547,14 @@
         <is>
           <t>NODE_S2007_08_0038</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -15330,6 +15588,12 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15344,6 +15608,14 @@
         <is>
           <t>NODE_S2007_08_0039</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -15377,6 +15649,8 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15391,6 +15665,14 @@
         <is>
           <t>NODE_S2007_08_0040</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -15518,6 +15800,8 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15532,6 +15816,14 @@
         <is>
           <t>NODE_S2007_08_0043</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -15659,6 +15951,12 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15673,6 +15971,14 @@
         <is>
           <t>NODE_S2007_08_0046</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -15753,6 +16059,12 @@
           <t>NODE_S2008_09_0048</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0050</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15762,6 +16074,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -15795,6 +16115,8 @@
           <t>NODE_S2008_09_0048</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15804,6 +16126,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -15884,6 +16214,12 @@
           <t>NODE_S2008_09_0051</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0053</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15898,6 +16234,14 @@
         <is>
           <t>NODE_S2007_08_0049</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -15931,6 +16275,8 @@
           <t>NODE_S2008_09_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15945,6 +16291,14 @@
         <is>
           <t>NODE_S2007_08_0050</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -16166,6 +16520,12 @@
           <t>NODE_S2008_09_0057</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0059</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16180,6 +16540,14 @@
         <is>
           <t>NODE_S2007_08_0054</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -16213,6 +16581,8 @@
           <t>NODE_S2008_09_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16227,6 +16597,14 @@
         <is>
           <t>NODE_S2007_08_0055</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -16480,6 +16858,12 @@
           <t>NODE_S2008_09_0064</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0066</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16494,6 +16878,14 @@
         <is>
           <t>NODE_S2007_08_0065</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -16527,6 +16919,8 @@
           <t>NODE_S2008_09_0064</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16536,6 +16930,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -16569,6 +16971,8 @@
           <t>NODE_S2008_09_0064</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16578,6 +16982,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -16826,6 +17238,12 @@
           <t>NODE_S2008_09_0071</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0074</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16840,6 +17258,14 @@
         <is>
           <t>NODE_S2007_08_0070</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -16873,6 +17299,8 @@
           <t>NODE_S2008_09_0071</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16882,6 +17310,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -16915,6 +17351,8 @@
           <t>NODE_S2008_09_0071</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16924,6 +17362,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -16973,6 +17419,8 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -17102,6 +17550,7 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -1141,6 +1141,11 @@
           <t>HC Energie Karlovy Vary</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F10" t="n">
         <v>52</v>
       </c>
@@ -14126,8 +14131,6 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14183,8 +14186,6 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14240,8 +14241,6 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14297,8 +14296,6 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14354,8 +14351,6 @@
           <t>NODE_S2008_09_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14411,8 +14406,6 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14468,8 +14461,6 @@
           <t>NODE_S2008_09_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14819,7 +14810,6 @@
           <t>NODE_S2008_09_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14880,7 +14870,6 @@
           <t>NODE_S2008_09_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14936,8 +14925,6 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14993,8 +14980,6 @@
           <t>NODE_S2008_09_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15532,7 +15517,6 @@
           <t>NODE_S2008_09_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15593,7 +15577,6 @@
           <t>NODE_S2008_09_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15649,8 +15632,6 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15800,8 +15781,6 @@
           <t>NODE_S2008_09_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15956,7 +15935,6 @@
           <t>NODE_S2008_09_0039</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16064,7 +16042,6 @@
           <t>NODE_S2008_09_0050</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16115,8 +16092,6 @@
           <t>NODE_S2008_09_0048</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16219,7 +16194,6 @@
           <t>NODE_S2008_09_0053</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16275,8 +16249,6 @@
           <t>NODE_S2008_09_0051</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16525,7 +16497,6 @@
           <t>NODE_S2008_09_0059</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16581,8 +16552,6 @@
           <t>NODE_S2008_09_0057</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16863,7 +16832,6 @@
           <t>NODE_S2008_09_0066</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16919,8 +16887,6 @@
           <t>NODE_S2008_09_0064</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16971,8 +16937,6 @@
           <t>NODE_S2008_09_0064</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17243,7 +17207,6 @@
           <t>NODE_S2008_09_0074</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17299,8 +17262,6 @@
           <t>NODE_S2008_09_0071</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17351,8 +17312,6 @@
           <t>NODE_S2008_09_0071</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17419,8 +17378,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -17550,7 +17507,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
@@ -33593,7 +33549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33773,6 +33729,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Energie Karlovy Vary</t>
         </is>
       </c>
     </row>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -17378,6 +17378,8 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -17507,6 +17509,7 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -5402,7 +5402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7575,6 +7575,635 @@
       <c r="V41" t="inlineStr">
         <is>
           <t>SER_S2008_09_0036</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0077</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0077</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0240</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0077</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0241</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sokol Semechnice</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0077</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0242</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0077</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0243</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0244</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0245</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0246</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0247</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0248</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0249</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0250</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0251</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0252</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00276</t>
         </is>
       </c>
     </row>
@@ -10540,7 +11169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12190,6 +12819,771 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HLC Bulldogs Brno</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0253</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VSK Technika Brno B</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0254</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SK Minerva Boskovice B</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0255</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sokol Velatice</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0256</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Zastávka u Brna</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0257</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TJ Tatran Hrušky</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0258</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Old Stars Uhersky Ostroh</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0259</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HC Napajedla</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0260</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HC Vizovice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0261</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HC Baťovka</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0262</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Rudí kohouti</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0263</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>KAS Napajedla</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0264</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BUM Zlín</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0265</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Lizzaran Šneci</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0266</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0267</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0268</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0269</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00293</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12201,7 +13595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12938,6 +14332,1723 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TJ Horní Benešov B</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0270</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ice Dogs Krnov</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0271</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC Rýmařov</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0272</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TS Batex Bruntál</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0273</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HC Lomnice</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0274</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SK Malá Morávka</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0275</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HC Grizzlies Rýmařov</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0276</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HC Tučňáci Krnov</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0277</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Rebyd Svobodné Heřmanovice</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0278</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HC Železná</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0279</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SK Medvědi Rýmařov</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0280</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HC Buly centrum Kravaře</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0281</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Auto Kuzník Opava</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0282</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SK Kravaře</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0283</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Draci Opava</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0284</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0285</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TJ Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0286</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0287</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0288</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HC Kozel Těškovice</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0289</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00313</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0290</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HC Jelen Kyjovice</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0291</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HC Stará Bělá</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0292</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HC Králíkáři Krásné Pole</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0293</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HC Vratimov</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0294</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SK Ostrava</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0295</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Jestřábi Třinec</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0296</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HC Krásné Pole</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0297</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Vikings TEAM Bohumín</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0298</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HC Sokol Stará Bělá</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0299</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HC Bohumín</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0300</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bar 66 Opava</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0301</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00325</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>STAR Ostrava</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0302</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00326</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Koksovna Ostrava</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0303</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00327</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>13</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HC Petřvald - Válcovny</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0304</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00328</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>14</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HC Bítov</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0305</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00329</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>15</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HC Venezia Ostrava</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0306</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00330</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VV Ostrava</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0307</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2008_09_00331</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13431,7 +16542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17535,6 +20646,134 @@
       <c r="A91" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0077</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0078</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0079</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Blansko</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0071</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0080</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Severomoravský – Bruntál</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>NODE_S2008_09_0076</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -24133,7 +27372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J226"/>
+  <dimension ref="A1:J294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -33538,6 +36777,2187 @@
       <c r="J226" t="inlineStr">
         <is>
           <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0240</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0241</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0242</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Sokol Semechnice</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Sokol Semechnice</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0243</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0244</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0245</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0246</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0247</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0248</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0249</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0250</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0251</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0252</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0253</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HLC Bulldogs Brno</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>HLC Bulldogs Brno</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0254</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>VSK Technika Brno B</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>VSK Technika Brno B</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0255</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>SK Minerva Boskovice B</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SK Minerva Boskovice B</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0256</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sokol Velatice</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Sokol Velatice</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0257</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HC Zastávka u Brna</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>HC Zastávka u Brna</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0258</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TJ Tatran Hrušky</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TJ Tatran Hrušky</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0259</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Old Stars Uhersky Ostroh</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Old Stars Uhersky Ostroh</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0260</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HC Napajedla</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>HC Napajedla</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0261</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HC Vizovice</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HC Vizovice</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0262</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HC Baťovka</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HC Baťovka</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0263</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Rudí kohouti</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Rudí kohouti</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0264</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>KAS Napajedla</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>KAS Napajedla</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0265</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>BUM Zlín</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>BUM Zlín</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0266</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Lizzaran Šneci</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Lizzaran Šneci</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0267</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0268</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0269</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0270</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TJ Horní Benešov B</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TJ Horní Benešov B</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0271</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Ice Dogs Krnov</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Ice Dogs Krnov</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0272</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HC Rýmařov</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>HC Rýmařov</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0273</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TS Batex Bruntál</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>TS Batex Bruntál</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0274</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HC Lomnice</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>HC Lomnice</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0275</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SK Malá Morávka</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SK Malá Morávka</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0276</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HC Grizzlies Rýmařov</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HC Grizzlies Rýmařov</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0277</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HC Tučňáci Krnov</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HC Tučňáci Krnov</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0278</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HC Rebyd Svobodné Heřmanovice</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HC Rebyd Svobodné Heřmanovice</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0279</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Železná</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Železná</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0280</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SK Medvědi Rýmařov</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SK Medvědi Rýmařov</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0281</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>HC Buly centrum Kravaře</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>HC Buly centrum Kravaře</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0282</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>HC Auto Kuzník Opava</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>HC Auto Kuzník Opava</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0283</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SK Kravaře</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SK Kravaře</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0284</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>HC Draci Opava</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>HC Draci Opava</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0285</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0286</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>TJ Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>TJ Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0287</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0288</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0289</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HC Kozel Těškovice</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HC Kozel Těškovice</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0290</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0291</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HC Jelen Kyjovice</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HC Jelen Kyjovice</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0292</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>HC Stará Bělá</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HC Stará Bělá</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0293</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>HC Králíkáři Krásné Pole</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>HC Králíkáři Krásné Pole</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0294</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>HC Vratimov</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HC Vratimov</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0295</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SK Ostrava</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SK Ostrava</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0296</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>HC Jestřábi Třinec</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>HC Jestřábi Třinec</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0297</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HC Krásné Pole</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>HC Krásné Pole</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0298</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Vikings TEAM Bohumín</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Vikings TEAM Bohumín</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0299</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HC Sokol Stará Bělá</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>HC Sokol Stará Bělá</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0300</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>HC Bohumín</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>HC Bohumín</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0301</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Bar 66 Opava</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Bar 66 Opava</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0302</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>STAR Ostrava</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>STAR Ostrava</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0303</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Koksovna Ostrava</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Koksovna Ostrava</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0304</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HC Petřvald - Válcovny</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>HC Petřvald - Válcovny</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0305</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HC Bítov</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>HC Bítov</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0306</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HC Venezia Ostrava</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HC Venezia Ostrava</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CLUB_S2008_09_0307</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>VV Ostrava</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>VV Ostrava</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -20489,8 +20489,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -20620,7 +20618,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
@@ -39235,7 +39232,7 @@
           <t>CLUB_S2008_09_0010</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39255,7 +39252,7 @@
           <t>CLUB_S2008_09_0017</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39275,7 +39272,7 @@
           <t>CLUB_S2008_09_0025</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39295,7 +39292,7 @@
           <t>CLUB_S2008_09_0053</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39315,7 +39312,7 @@
           <t>CLUB_S2008_09_0057</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39335,7 +39332,7 @@
           <t>CLUB_S2008_09_0058</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -39355,7 +39352,7 @@
           <t>CLUB_S2008_09_0060</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39375,7 +39372,7 @@
           <t>CLUB_S2008_09_0061</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Predators Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39395,7 +39392,7 @@
           <t>CLUB_S2008_09_0065</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39415,7 +39412,7 @@
           <t>CLUB_S2008_09_0078</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Valašský hokejový klub Vsetín' → 'Vsetín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39435,7 +39432,7 @@
           <t>CLUB_S2008_09_0080</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39455,7 +39452,7 @@
           <t>CLUB_S2008_09_0094</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39475,7 +39472,7 @@
           <t>CLUB_S2008_09_0114</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39495,7 +39492,7 @@
           <t>CLUB_S2008_09_0126</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39515,7 +39512,7 @@
           <t>CLUB_S2008_09_0135</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -39535,7 +39532,7 @@
           <t>CLUB_S2008_09_0142</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -39555,7 +39552,7 @@
           <t>CLUB_S2008_09_0158</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -39575,7 +39572,7 @@
           <t>CLUB_S2008_09_0161</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39595,7 +39592,7 @@
           <t>CLUB_S2008_09_0162</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39615,7 +39612,7 @@
           <t>CLUB_S2008_09_0165</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39635,7 +39632,7 @@
           <t>CLUB_S2008_09_0167</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -39655,7 +39652,7 @@
           <t>CLUB_S2008_09_0177</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -39675,7 +39672,7 @@
           <t>CLUB_S2008_09_0206</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2007_08_0119 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -39695,7 +39692,7 @@
           <t>CLUB_S2008_09_0213</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
@@ -39715,7 +39712,7 @@
           <t>NODE_S2008_09_0030</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
@@ -39735,7 +39732,7 @@
           <t>NODE_S2008_09_0031</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
@@ -39755,7 +39752,7 @@
           <t>NODE_S2008_09_0032</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -18222,7 +18222,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  Skupina A</t>
+          <t>KVAL Skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  Skupina B</t>
+          <t>KVAL Skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KVAL  Skupina C</t>
+          <t>KVAL Skupina C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -19125,7 +19125,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Finále</t>
+          <t>Středočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -19277,7 +19277,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19439,7 +19439,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40</t>
+          <t>Ústecký-Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 základní část</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 základní část</t>
+          <t>Liberecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -19640,7 +19640,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 Finále</t>
+          <t>Liberecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina A</t>
+          <t>Hradecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19915,7 +19915,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 základní část</t>
+          <t>Vysočina, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 Jihlava</t>
+          <t>Vysočina, 4. úroveň Jihlava</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Jihomoravský a Zlínský krajský přebor</t>
+          <t>Jihomoravský, 4. úroveň Jihomoravský a Zlínský krajský přebor</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20450,7 +20450,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -20489,6 +20489,8 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -20521,7 +20523,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -20618,6 +20620,7 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>

--- a/data/S2008_09_FINAL.xlsx
+++ b/data/S2008_09_FINAL.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -20489,8 +20489,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -20620,7 +20618,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
@@ -25136,7 +25133,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -25214,7 +25211,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -25292,7 +25289,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -25370,7 +25367,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -25453,7 +25450,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -25531,7 +25528,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -25609,7 +25606,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -25687,7 +25684,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -25765,7 +25762,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -25843,7 +25840,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -25921,7 +25918,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -26004,7 +26001,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -26082,7 +26079,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -26160,7 +26157,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -26238,7 +26235,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -26311,7 +26308,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
